--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N422"/>
+  <dimension ref="A1:N423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20684,6 +20684,54 @@
       <c r="N422" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>397.58</v>
+      </c>
+      <c r="C423" t="n">
+        <v>394.99</v>
+      </c>
+      <c r="D423" t="n">
+        <v>392.57</v>
+      </c>
+      <c r="E423" t="n">
+        <v>396.55</v>
+      </c>
+      <c r="F423" t="n">
+        <v>416.74</v>
+      </c>
+      <c r="G423" t="n">
+        <v>420.71</v>
+      </c>
+      <c r="H423" t="n">
+        <v>412.12</v>
+      </c>
+      <c r="I423" t="n">
+        <v>411.77</v>
+      </c>
+      <c r="J423" t="n">
+        <v>412.54</v>
+      </c>
+      <c r="K423" t="n">
+        <v>415.54</v>
+      </c>
+      <c r="L423" t="n">
+        <v>406.77</v>
+      </c>
+      <c r="M423" t="n">
+        <v>404.56</v>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20698,7 +20746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B496"/>
+  <dimension ref="A1:B497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25661,6 +25709,16 @@
       </c>
       <c r="B496" t="n">
         <v>-0.17</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -25829,28 +25887,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006911510455799498</v>
+        <v>0.002980863580339433</v>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001194543168765438</v>
+        <v>2.220107454531384e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.677428903160759</v>
+        <v>3.692427017288434</v>
       </c>
       <c r="N2" t="n">
-        <v>22.68192452536893</v>
+        <v>22.77983337924406</v>
       </c>
       <c r="O2" t="n">
-        <v>4.762554411801395</v>
+        <v>4.772822370384641</v>
       </c>
       <c r="P2" t="n">
-        <v>405.4076522850673</v>
+        <v>405.4458172367387</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25907,28 +25965,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05591273154948728</v>
+        <v>0.0519496158644286</v>
       </c>
       <c r="J3" t="n">
+        <v>422</v>
+      </c>
+      <c r="K3" t="n">
         <v>421</v>
       </c>
-      <c r="K3" t="n">
-        <v>420</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.006080806992945886</v>
+        <v>0.005255716790069975</v>
       </c>
       <c r="M3" t="n">
-        <v>4.131348939188383</v>
+        <v>4.144421823512959</v>
       </c>
       <c r="N3" t="n">
-        <v>29.32401610985712</v>
+        <v>29.41145733158775</v>
       </c>
       <c r="O3" t="n">
-        <v>5.415165381579506</v>
+        <v>5.423233106882623</v>
       </c>
       <c r="P3" t="n">
-        <v>401.6838467333922</v>
+        <v>401.7219007431756</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25985,28 +26043,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08253666018038187</v>
+        <v>0.07613144111610366</v>
       </c>
       <c r="J4" t="n">
+        <v>422</v>
+      </c>
+      <c r="K4" t="n">
         <v>421</v>
       </c>
-      <c r="K4" t="n">
-        <v>420</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.009979523944114055</v>
+        <v>0.008462917247300084</v>
       </c>
       <c r="M4" t="n">
-        <v>4.833809861474881</v>
+        <v>4.855727594461326</v>
       </c>
       <c r="N4" t="n">
-        <v>38.78290236758347</v>
+        <v>39.10113233431895</v>
       </c>
       <c r="O4" t="n">
-        <v>6.227592020001268</v>
+        <v>6.25308982298503</v>
       </c>
       <c r="P4" t="n">
-        <v>403.6018835835545</v>
+        <v>403.6633867765739</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26063,28 +26121,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04836569570581702</v>
+        <v>0.04153106309888559</v>
       </c>
       <c r="J5" t="n">
+        <v>422</v>
+      </c>
+      <c r="K5" t="n">
         <v>421</v>
       </c>
-      <c r="K5" t="n">
-        <v>420</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.003299139554795105</v>
+        <v>0.002420811870839534</v>
       </c>
       <c r="M5" t="n">
-        <v>4.858746227612301</v>
+        <v>4.880087080153452</v>
       </c>
       <c r="N5" t="n">
-        <v>40.55563414866966</v>
+        <v>40.92651850841958</v>
       </c>
       <c r="O5" t="n">
-        <v>6.368330562138688</v>
+        <v>6.397383723712341</v>
       </c>
       <c r="P5" t="n">
-        <v>409.3617966655105</v>
+        <v>409.4274231061088</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26141,28 +26199,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08277452273315597</v>
+        <v>0.07664836787508558</v>
       </c>
       <c r="J6" t="n">
+        <v>422</v>
+      </c>
+      <c r="K6" t="n">
         <v>421</v>
       </c>
-      <c r="K6" t="n">
-        <v>420</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01047054147515858</v>
+        <v>0.008952919339359933</v>
       </c>
       <c r="M6" t="n">
-        <v>4.78249793930556</v>
+        <v>4.799989395361909</v>
       </c>
       <c r="N6" t="n">
-        <v>37.15909505070672</v>
+        <v>37.44620442530831</v>
       </c>
       <c r="O6" t="n">
-        <v>6.095826035141318</v>
+        <v>6.11933039027215</v>
       </c>
       <c r="P6" t="n">
-        <v>427.1906582328156</v>
+        <v>427.2494818391469</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26219,28 +26277,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02714916744077807</v>
+        <v>0.02080069325226937</v>
       </c>
       <c r="J7" t="n">
+        <v>422</v>
+      </c>
+      <c r="K7" t="n">
         <v>421</v>
       </c>
-      <c r="K7" t="n">
-        <v>420</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.000959980656729309</v>
+        <v>0.0005618271836890232</v>
       </c>
       <c r="M7" t="n">
-        <v>5.208206905639789</v>
+        <v>5.229514304213737</v>
       </c>
       <c r="N7" t="n">
-        <v>44.01955086431422</v>
+        <v>44.3181037122665</v>
       </c>
       <c r="O7" t="n">
-        <v>6.634723118888551</v>
+        <v>6.657184368204511</v>
       </c>
       <c r="P7" t="n">
-        <v>433.0763019564631</v>
+        <v>433.1372602827088</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26297,28 +26355,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05731692205448192</v>
+        <v>0.05230461678891275</v>
       </c>
       <c r="J8" t="n">
+        <v>422</v>
+      </c>
+      <c r="K8" t="n">
         <v>421</v>
       </c>
-      <c r="K8" t="n">
-        <v>420</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.004511201959083722</v>
+        <v>0.003758429451445777</v>
       </c>
       <c r="M8" t="n">
-        <v>5.09877607410287</v>
+        <v>5.111528509964361</v>
       </c>
       <c r="N8" t="n">
-        <v>41.60274627371702</v>
+        <v>41.75520999762327</v>
       </c>
       <c r="O8" t="n">
-        <v>6.450019090957563</v>
+        <v>6.461827140803386</v>
       </c>
       <c r="P8" t="n">
-        <v>420.9440347836579</v>
+        <v>420.9921631575866</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26375,28 +26433,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06262419026021085</v>
+        <v>0.05873050541609194</v>
       </c>
       <c r="J9" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K9" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006281225367309018</v>
+        <v>0.005536782707270982</v>
       </c>
       <c r="M9" t="n">
-        <v>4.760428818028606</v>
+        <v>4.768645898035213</v>
       </c>
       <c r="N9" t="n">
-        <v>35.5225317037028</v>
+        <v>35.58958219590203</v>
       </c>
       <c r="O9" t="n">
-        <v>5.960078162549783</v>
+        <v>5.965700478225673</v>
       </c>
       <c r="P9" t="n">
-        <v>418.1454838265432</v>
+        <v>418.1829093333251</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26453,28 +26511,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06887954221080196</v>
+        <v>0.06517881478102375</v>
       </c>
       <c r="J10" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K10" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007320317406308674</v>
+        <v>0.006573120255302767</v>
       </c>
       <c r="M10" t="n">
-        <v>4.925723654860443</v>
+        <v>4.931167912013315</v>
       </c>
       <c r="N10" t="n">
-        <v>36.83496566818371</v>
+        <v>36.88428894398988</v>
       </c>
       <c r="O10" t="n">
-        <v>6.069181630844781</v>
+        <v>6.073243692129427</v>
       </c>
       <c r="P10" t="n">
-        <v>418.3527120901977</v>
+        <v>418.3882829196474</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26531,28 +26589,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1559403665236624</v>
+        <v>0.1546422869823982</v>
       </c>
       <c r="J11" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K11" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03440298188861213</v>
+        <v>0.0340260690441736</v>
       </c>
       <c r="M11" t="n">
-        <v>5.031348051359316</v>
+        <v>5.025483652407261</v>
       </c>
       <c r="N11" t="n">
-        <v>39.07666348749409</v>
+        <v>39.00087255076711</v>
       </c>
       <c r="O11" t="n">
-        <v>6.251132976308702</v>
+        <v>6.245067857979376</v>
       </c>
       <c r="P11" t="n">
-        <v>414.1206716070126</v>
+        <v>414.133148550222</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26609,28 +26667,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1076282541083678</v>
+        <v>0.1047036889143073</v>
       </c>
       <c r="J12" t="n">
+        <v>422</v>
+      </c>
+      <c r="K12" t="n">
         <v>421</v>
       </c>
-      <c r="K12" t="n">
-        <v>420</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01543395593007268</v>
+        <v>0.01467255505134879</v>
       </c>
       <c r="M12" t="n">
-        <v>5.25587585075183</v>
+        <v>5.25655791091507</v>
       </c>
       <c r="N12" t="n">
-        <v>42.14376675276323</v>
+        <v>42.12853729675167</v>
       </c>
       <c r="O12" t="n">
-        <v>6.491823068504195</v>
+        <v>6.490649990313117</v>
       </c>
       <c r="P12" t="n">
-        <v>409.9418700037064</v>
+        <v>409.9700857891206</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26687,28 +26745,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3138644046213215</v>
+        <v>0.3126026141933924</v>
       </c>
       <c r="J13" t="n">
+        <v>422</v>
+      </c>
+      <c r="K13" t="n">
         <v>421</v>
       </c>
-      <c r="K13" t="n">
-        <v>420</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09150753226608888</v>
+        <v>0.09129320261561502</v>
       </c>
       <c r="M13" t="n">
-        <v>6.00771903626164</v>
+        <v>5.999923485758789</v>
       </c>
       <c r="N13" t="n">
-        <v>55.63988590306269</v>
+        <v>55.5234598014268</v>
       </c>
       <c r="O13" t="n">
-        <v>7.459214831539757</v>
+        <v>7.45140656530207</v>
       </c>
       <c r="P13" t="n">
-        <v>398.9007640746137</v>
+        <v>398.9129566885354</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26746,7 +26804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N422"/>
+  <dimension ref="A1:N423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57085,6 +57143,78 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-34.80143668349004,173.38883243852555</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-34.801503102660334,173.38971029320612</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-34.801514421214605,173.39057660050224</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-34.80137653624464,173.391450840298</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-34.80115827174023,173.39228911852723</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-34.80096535394408,173.39300659010001</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-34.80069063128728,173.39375540519703</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-34.8003382348604,173.3945243345323</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-34.79995217791183,173.3952197210667</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-34.79948548058799,173.39580602372197</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-34.7990248613689,173.39642172468095</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-34.79845475857091,173.39692127075028</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N423"/>
+  <dimension ref="A1:N424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20730,6 +20730,54 @@
         <v>404.56</v>
       </c>
       <c r="N423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="C424" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="D424" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="E424" t="n">
+        <v>397.44</v>
+      </c>
+      <c r="F424" t="n">
+        <v>417.3</v>
+      </c>
+      <c r="G424" t="n">
+        <v>421.83</v>
+      </c>
+      <c r="H424" t="n">
+        <v>412.85</v>
+      </c>
+      <c r="I424" t="n">
+        <v>412.22</v>
+      </c>
+      <c r="J424" t="n">
+        <v>413.64</v>
+      </c>
+      <c r="K424" t="n">
+        <v>416.42</v>
+      </c>
+      <c r="L424" t="n">
+        <v>407.04</v>
+      </c>
+      <c r="M424" t="n">
+        <v>405.78</v>
+      </c>
+      <c r="N424" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20746,7 +20794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B497"/>
+  <dimension ref="A1:B498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25719,6 +25767,16 @@
       </c>
       <c r="B497" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -25887,28 +25945,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002980863580339433</v>
+        <v>-0.0006868991246921331</v>
       </c>
       <c r="J2" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>2.220107454531384e-05</v>
+        <v>1.178796396383852e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.692427017288434</v>
+        <v>3.705808372386401</v>
       </c>
       <c r="N2" t="n">
-        <v>22.77983337924406</v>
+        <v>22.85881658991201</v>
       </c>
       <c r="O2" t="n">
-        <v>4.772822370384641</v>
+        <v>4.781089477296153</v>
       </c>
       <c r="P2" t="n">
-        <v>405.4458172367387</v>
+        <v>405.4814964999647</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25965,28 +26023,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0519496158644286</v>
+        <v>0.0476786444958588</v>
       </c>
       <c r="J3" t="n">
+        <v>423</v>
+      </c>
+      <c r="K3" t="n">
         <v>422</v>
       </c>
-      <c r="K3" t="n">
-        <v>421</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.005255716790069975</v>
+        <v>0.004428454083434286</v>
       </c>
       <c r="M3" t="n">
-        <v>4.144421823512959</v>
+        <v>4.159119977895007</v>
       </c>
       <c r="N3" t="n">
-        <v>29.41145733158775</v>
+        <v>29.52538361164523</v>
       </c>
       <c r="O3" t="n">
-        <v>5.423233106882623</v>
+        <v>5.433726494004389</v>
       </c>
       <c r="P3" t="n">
-        <v>401.7219007431756</v>
+        <v>401.7629883322708</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26043,28 +26101,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07613144111610366</v>
+        <v>0.06965382432176841</v>
       </c>
       <c r="J4" t="n">
+        <v>423</v>
+      </c>
+      <c r="K4" t="n">
         <v>422</v>
       </c>
-      <c r="K4" t="n">
-        <v>421</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.008462917247300084</v>
+        <v>0.00705837764057593</v>
       </c>
       <c r="M4" t="n">
-        <v>4.855727594461326</v>
+        <v>4.877990571997774</v>
       </c>
       <c r="N4" t="n">
-        <v>39.10113233431895</v>
+        <v>39.43085347035349</v>
       </c>
       <c r="O4" t="n">
-        <v>6.25308982298503</v>
+        <v>6.279399132907025</v>
       </c>
       <c r="P4" t="n">
-        <v>403.6633867765739</v>
+        <v>403.7257027310006</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26121,28 +26179,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04153106309888559</v>
+        <v>0.03521265454204128</v>
       </c>
       <c r="J5" t="n">
+        <v>423</v>
+      </c>
+      <c r="K5" t="n">
         <v>422</v>
       </c>
-      <c r="K5" t="n">
-        <v>421</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.002420811870839534</v>
+        <v>0.001734374648439285</v>
       </c>
       <c r="M5" t="n">
-        <v>4.880087080153452</v>
+        <v>4.899561928690723</v>
       </c>
       <c r="N5" t="n">
-        <v>40.92651850841958</v>
+        <v>41.23140665400116</v>
       </c>
       <c r="O5" t="n">
-        <v>6.397383723712341</v>
+        <v>6.421168636159711</v>
       </c>
       <c r="P5" t="n">
-        <v>409.4274231061088</v>
+        <v>409.4882074458095</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26199,28 +26257,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07664836787508558</v>
+        <v>0.07086513459241435</v>
       </c>
       <c r="J6" t="n">
+        <v>423</v>
+      </c>
+      <c r="K6" t="n">
         <v>422</v>
       </c>
-      <c r="K6" t="n">
-        <v>421</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.008952919339359933</v>
+        <v>0.00763816098470127</v>
       </c>
       <c r="M6" t="n">
-        <v>4.799989395361909</v>
+        <v>4.815826349273316</v>
       </c>
       <c r="N6" t="n">
-        <v>37.44620442530831</v>
+        <v>37.69414525989995</v>
       </c>
       <c r="O6" t="n">
-        <v>6.11933039027215</v>
+        <v>6.139555786854611</v>
       </c>
       <c r="P6" t="n">
-        <v>427.2494818391469</v>
+        <v>427.3051176868861</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26277,28 +26335,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02080069325226937</v>
+        <v>0.015073771278845</v>
       </c>
       <c r="J7" t="n">
+        <v>423</v>
+      </c>
+      <c r="K7" t="n">
         <v>422</v>
       </c>
-      <c r="K7" t="n">
-        <v>421</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0005618271836890232</v>
+        <v>0.0002946195267138352</v>
       </c>
       <c r="M7" t="n">
-        <v>5.229514304213737</v>
+        <v>5.247633019587443</v>
       </c>
       <c r="N7" t="n">
-        <v>44.3181037122665</v>
+        <v>44.54323592232839</v>
       </c>
       <c r="O7" t="n">
-        <v>6.657184368204511</v>
+        <v>6.674071914680602</v>
       </c>
       <c r="P7" t="n">
-        <v>433.1372602827088</v>
+        <v>433.1923544045181</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26355,28 +26413,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05230461678891275</v>
+        <v>0.04770379474503079</v>
       </c>
       <c r="J8" t="n">
+        <v>423</v>
+      </c>
+      <c r="K8" t="n">
         <v>422</v>
       </c>
-      <c r="K8" t="n">
-        <v>421</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.003758429451445777</v>
+        <v>0.003130224979419838</v>
       </c>
       <c r="M8" t="n">
-        <v>5.111528509964361</v>
+        <v>5.122158405356881</v>
       </c>
       <c r="N8" t="n">
-        <v>41.75520999762327</v>
+        <v>41.86934341905234</v>
       </c>
       <c r="O8" t="n">
-        <v>6.461827140803386</v>
+        <v>6.47065247243679</v>
       </c>
       <c r="P8" t="n">
-        <v>420.9921631575866</v>
+        <v>421.0364239754019</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26433,28 +26491,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05873050541609194</v>
+        <v>0.05510188630158961</v>
       </c>
       <c r="J9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005536782707270982</v>
+        <v>0.00488674078917295</v>
       </c>
       <c r="M9" t="n">
-        <v>4.768645898035213</v>
+        <v>4.775744608285412</v>
       </c>
       <c r="N9" t="n">
-        <v>35.58958219590203</v>
+        <v>35.63762867294041</v>
       </c>
       <c r="O9" t="n">
-        <v>5.965700478225673</v>
+        <v>5.969726013222082</v>
       </c>
       <c r="P9" t="n">
-        <v>418.1829093333251</v>
+        <v>418.2178527607317</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26511,28 +26569,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06517881478102375</v>
+        <v>0.06205719006191729</v>
       </c>
       <c r="J10" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K10" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006573120255302767</v>
+        <v>0.005980468966839569</v>
       </c>
       <c r="M10" t="n">
-        <v>4.931167912013315</v>
+        <v>4.933882079934437</v>
       </c>
       <c r="N10" t="n">
-        <v>36.88428894398988</v>
+        <v>36.8949177337435</v>
       </c>
       <c r="O10" t="n">
-        <v>6.073243692129427</v>
+        <v>6.074118679589945</v>
       </c>
       <c r="P10" t="n">
-        <v>418.3882829196474</v>
+        <v>418.4183440154308</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26589,28 +26647,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1546422869823982</v>
+        <v>0.1537797252560373</v>
       </c>
       <c r="J11" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K11" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0340260690441736</v>
+        <v>0.03384073379506936</v>
       </c>
       <c r="M11" t="n">
-        <v>5.025483652407261</v>
+        <v>5.017604427965765</v>
       </c>
       <c r="N11" t="n">
-        <v>39.00087255076711</v>
+        <v>38.91614106891124</v>
       </c>
       <c r="O11" t="n">
-        <v>6.245067857979376</v>
+        <v>6.238280297398575</v>
       </c>
       <c r="P11" t="n">
-        <v>414.133148550222</v>
+        <v>414.1414549781268</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26667,28 +26725,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1047036889143073</v>
+        <v>0.1019450336617525</v>
       </c>
       <c r="J12" t="n">
+        <v>423</v>
+      </c>
+      <c r="K12" t="n">
         <v>422</v>
       </c>
-      <c r="K12" t="n">
-        <v>421</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01467255505134879</v>
+        <v>0.01397418912877146</v>
       </c>
       <c r="M12" t="n">
-        <v>5.25655791091507</v>
+        <v>5.256444196254459</v>
       </c>
       <c r="N12" t="n">
-        <v>42.12853729675167</v>
+        <v>42.10471019493107</v>
       </c>
       <c r="O12" t="n">
-        <v>6.490649990313117</v>
+        <v>6.488814236432653</v>
       </c>
       <c r="P12" t="n">
-        <v>409.9700857891206</v>
+        <v>409.9967508951393</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26745,28 +26803,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3126026141933924</v>
+        <v>0.3119414732559191</v>
       </c>
       <c r="J13" t="n">
+        <v>423</v>
+      </c>
+      <c r="K13" t="n">
         <v>422</v>
       </c>
-      <c r="K13" t="n">
-        <v>421</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09129320261561502</v>
+        <v>0.09141179835563962</v>
       </c>
       <c r="M13" t="n">
-        <v>5.999923485758789</v>
+        <v>5.98907808007761</v>
       </c>
       <c r="N13" t="n">
-        <v>55.5234598014268</v>
+        <v>55.39623547914542</v>
       </c>
       <c r="O13" t="n">
-        <v>7.45140656530207</v>
+        <v>7.44286473605059</v>
       </c>
       <c r="P13" t="n">
-        <v>398.9129566885354</v>
+        <v>398.9193572215266</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26804,7 +26862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N423"/>
+  <dimension ref="A1:N424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57215,6 +57273,78 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-34.80143272215935,173.38883271187092</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-34.8015097744379,173.3897101370639</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-34.80151720762852,173.39057687283665</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-34.80136855128643,173.3914498616612</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-34.80115328868505,173.39228812607752</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-34.80095605186133,173.39300182103275</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-34.80068493627309,173.39375140263124</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-34.80033478370992,173.3945217468291</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-34.79994435499553,173.39521232749985</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-34.79947993421365,173.39579914355718</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-34.79902338366216,173.39641937886302</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-34.79844861658632,173.39691020592318</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N424"/>
+  <dimension ref="A1:N427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20780,6 +20780,150 @@
       <c r="N424" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="C425" t="n">
+        <v>391.83</v>
+      </c>
+      <c r="D425" t="n">
+        <v>391.41</v>
+      </c>
+      <c r="E425" t="n">
+        <v>396.78</v>
+      </c>
+      <c r="F425" t="n">
+        <v>415.93</v>
+      </c>
+      <c r="G425" t="n">
+        <v>421.77</v>
+      </c>
+      <c r="H425" t="n">
+        <v>411.6</v>
+      </c>
+      <c r="I425" t="n">
+        <v>412.73</v>
+      </c>
+      <c r="J425" t="n">
+        <v>413.96</v>
+      </c>
+      <c r="K425" t="n">
+        <v>418.02</v>
+      </c>
+      <c r="L425" t="n">
+        <v>406.08</v>
+      </c>
+      <c r="M425" t="n">
+        <v>403.76</v>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>394.21</v>
+      </c>
+      <c r="C426" t="n">
+        <v>391.53</v>
+      </c>
+      <c r="D426" t="n">
+        <v>391.72</v>
+      </c>
+      <c r="E426" t="n">
+        <v>397.6</v>
+      </c>
+      <c r="F426" t="n">
+        <v>417.11</v>
+      </c>
+      <c r="G426" t="n">
+        <v>422.44</v>
+      </c>
+      <c r="H426" t="n">
+        <v>412.45</v>
+      </c>
+      <c r="I426" t="n">
+        <v>412.58</v>
+      </c>
+      <c r="J426" t="n">
+        <v>414.84</v>
+      </c>
+      <c r="K426" t="n">
+        <v>418.05</v>
+      </c>
+      <c r="L426" t="n">
+        <v>407.47</v>
+      </c>
+      <c r="M426" t="n">
+        <v>405.2</v>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>394.57</v>
+      </c>
+      <c r="C427" t="n">
+        <v>392.66</v>
+      </c>
+      <c r="D427" t="n">
+        <v>393.06</v>
+      </c>
+      <c r="E427" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="F427" t="n">
+        <v>418.38</v>
+      </c>
+      <c r="G427" t="n">
+        <v>423.64</v>
+      </c>
+      <c r="H427" t="n">
+        <v>413.49</v>
+      </c>
+      <c r="I427" t="n">
+        <v>413.63</v>
+      </c>
+      <c r="J427" t="n">
+        <v>415.27</v>
+      </c>
+      <c r="K427" t="n">
+        <v>418.13</v>
+      </c>
+      <c r="L427" t="n">
+        <v>408.41</v>
+      </c>
+      <c r="M427" t="n">
+        <v>405.77</v>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25777,6 +25921,36 @@
       </c>
       <c r="B498" t="n">
         <v>0.98</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>-0.22</v>
       </c>
     </row>
   </sheetData>
@@ -25945,28 +26119,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0006868991246921331</v>
+        <v>-0.01728096325378121</v>
       </c>
       <c r="J2" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K2" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L2" t="n">
-        <v>1.178796396383852e-06</v>
+        <v>0.0007288064474882949</v>
       </c>
       <c r="M2" t="n">
-        <v>3.705808372386401</v>
+        <v>3.783209756166442</v>
       </c>
       <c r="N2" t="n">
-        <v>22.85881658991201</v>
+        <v>23.61866515467909</v>
       </c>
       <c r="O2" t="n">
-        <v>4.781089477296153</v>
+        <v>4.859903821546173</v>
       </c>
       <c r="P2" t="n">
-        <v>405.4814964999647</v>
+        <v>405.6435162661929</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26023,28 +26197,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0476786444958588</v>
+        <v>0.03197687071442317</v>
       </c>
       <c r="J3" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004428454083434286</v>
+        <v>0.00197480151307694</v>
       </c>
       <c r="M3" t="n">
-        <v>4.159119977895007</v>
+        <v>4.219894876002459</v>
       </c>
       <c r="N3" t="n">
-        <v>29.52538361164523</v>
+        <v>30.15450734880264</v>
       </c>
       <c r="O3" t="n">
-        <v>5.433726494004389</v>
+        <v>5.491311987931722</v>
       </c>
       <c r="P3" t="n">
-        <v>401.7629883322708</v>
+        <v>401.9146072700453</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26101,28 +26275,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06965382432176841</v>
+        <v>0.05040404409291393</v>
       </c>
       <c r="J4" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K4" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00705837764057593</v>
+        <v>0.003654984816690132</v>
       </c>
       <c r="M4" t="n">
-        <v>4.877990571997774</v>
+        <v>4.947404150840043</v>
       </c>
       <c r="N4" t="n">
-        <v>39.43085347035349</v>
+        <v>40.41263802403256</v>
       </c>
       <c r="O4" t="n">
-        <v>6.279399132907025</v>
+        <v>6.357093520157822</v>
       </c>
       <c r="P4" t="n">
-        <v>403.7257027310006</v>
+        <v>403.9115790086503</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26179,28 +26353,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03521265454204128</v>
+        <v>0.01698752184509155</v>
       </c>
       <c r="J5" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K5" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001734374648439285</v>
+        <v>0.0004001050342025136</v>
       </c>
       <c r="M5" t="n">
-        <v>4.899561928690723</v>
+        <v>4.956566098775682</v>
       </c>
       <c r="N5" t="n">
-        <v>41.23140665400116</v>
+        <v>42.07019282788725</v>
       </c>
       <c r="O5" t="n">
-        <v>6.421168636159711</v>
+        <v>6.486153931868041</v>
       </c>
       <c r="P5" t="n">
-        <v>409.4882074458095</v>
+        <v>409.6641889766165</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26257,28 +26431,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07086513459241435</v>
+        <v>0.05371411892306538</v>
       </c>
       <c r="J6" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K6" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00763816098470127</v>
+        <v>0.004361545018473634</v>
       </c>
       <c r="M6" t="n">
-        <v>4.815826349273316</v>
+        <v>4.863929067067928</v>
       </c>
       <c r="N6" t="n">
-        <v>37.69414525989995</v>
+        <v>38.43266280477985</v>
       </c>
       <c r="O6" t="n">
-        <v>6.139555786854611</v>
+        <v>6.199408262469882</v>
       </c>
       <c r="P6" t="n">
-        <v>427.3051176868861</v>
+        <v>427.4707239815837</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26335,28 +26509,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>0.015073771278845</v>
+        <v>-0.0005655593466930168</v>
       </c>
       <c r="J7" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K7" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002946195267138352</v>
+        <v>4.141937536283891e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>5.247633019587443</v>
+        <v>5.294521965019835</v>
       </c>
       <c r="N7" t="n">
-        <v>44.54323592232839</v>
+        <v>45.06246067455279</v>
       </c>
       <c r="O7" t="n">
-        <v>6.674071914680602</v>
+        <v>6.712857861935763</v>
       </c>
       <c r="P7" t="n">
-        <v>433.1923544045181</v>
+        <v>433.3433657856941</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26413,28 +26587,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04770379474503079</v>
+        <v>0.03376216806224351</v>
       </c>
       <c r="J8" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K8" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003130224979419838</v>
+        <v>0.001572335334793062</v>
       </c>
       <c r="M8" t="n">
-        <v>5.122158405356881</v>
+        <v>5.155468375283181</v>
       </c>
       <c r="N8" t="n">
-        <v>41.86934341905234</v>
+        <v>42.23712477164677</v>
       </c>
       <c r="O8" t="n">
-        <v>6.47065247243679</v>
+        <v>6.499009522353908</v>
       </c>
       <c r="P8" t="n">
-        <v>421.0364239754019</v>
+        <v>421.1710415969687</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26491,28 +26665,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05510188630158961</v>
+        <v>0.0455624436120507</v>
       </c>
       <c r="J9" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K9" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00488674078917295</v>
+        <v>0.003374393103692142</v>
       </c>
       <c r="M9" t="n">
-        <v>4.775744608285412</v>
+        <v>4.790638534972449</v>
       </c>
       <c r="N9" t="n">
-        <v>35.63762867294041</v>
+        <v>35.6958887580976</v>
       </c>
       <c r="O9" t="n">
-        <v>5.969726013222082</v>
+        <v>5.974603648619514</v>
       </c>
       <c r="P9" t="n">
-        <v>418.2178527607317</v>
+        <v>418.3100576040718</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26569,28 +26743,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06205719006191729</v>
+        <v>0.05440263671690847</v>
       </c>
       <c r="J10" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K10" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005980468966839569</v>
+        <v>0.00465603371822354</v>
       </c>
       <c r="M10" t="n">
-        <v>4.933882079934437</v>
+        <v>4.935334624740664</v>
       </c>
       <c r="N10" t="n">
-        <v>36.8949177337435</v>
+        <v>36.83534873596013</v>
       </c>
       <c r="O10" t="n">
-        <v>6.074118679589945</v>
+        <v>6.069213189200074</v>
       </c>
       <c r="P10" t="n">
-        <v>418.4183440154308</v>
+        <v>418.4923276134031</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26647,28 +26821,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1537797252560373</v>
+        <v>0.1535890930392694</v>
       </c>
       <c r="J11" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K11" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03384073379506936</v>
+        <v>0.03432095108734368</v>
       </c>
       <c r="M11" t="n">
-        <v>5.017604427965765</v>
+        <v>4.983141239583077</v>
       </c>
       <c r="N11" t="n">
-        <v>38.91614106891124</v>
+        <v>38.64221948657276</v>
       </c>
       <c r="O11" t="n">
-        <v>6.238280297398575</v>
+        <v>6.216286631629268</v>
       </c>
       <c r="P11" t="n">
-        <v>414.1414549781268</v>
+        <v>414.1432971952908</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26725,28 +26899,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1019450336617525</v>
+        <v>0.09426536674434768</v>
       </c>
       <c r="J12" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K12" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01397418912877146</v>
+        <v>0.01211759455805272</v>
       </c>
       <c r="M12" t="n">
-        <v>5.256444196254459</v>
+        <v>5.253427831140098</v>
       </c>
       <c r="N12" t="n">
-        <v>42.10471019493107</v>
+        <v>42.0124092656825</v>
       </c>
       <c r="O12" t="n">
-        <v>6.488814236432653</v>
+        <v>6.481698023333276</v>
       </c>
       <c r="P12" t="n">
-        <v>409.9967508951393</v>
+        <v>410.071249740818</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26803,28 +26977,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3119414732559191</v>
+        <v>0.308728777497979</v>
       </c>
       <c r="J13" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K13" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09141179835563962</v>
+        <v>0.09105502918686625</v>
       </c>
       <c r="M13" t="n">
-        <v>5.98907808007761</v>
+        <v>5.962967312340115</v>
       </c>
       <c r="N13" t="n">
-        <v>55.39623547914542</v>
+        <v>55.04478812015495</v>
       </c>
       <c r="O13" t="n">
-        <v>7.44286473605059</v>
+        <v>7.419217487050433</v>
       </c>
       <c r="P13" t="n">
-        <v>398.9193572215266</v>
+        <v>398.9505666420069</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26862,7 +27036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N424"/>
+  <dimension ref="A1:N427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57345,6 +57519,222 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-34.80147719709927,173.38882964294658</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-34.801531592953644,173.3897096264364</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-34.80152484779566,173.39057761956008</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-34.80137447271611,173.39145058739183</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-34.80116547937358,173.39229055403507</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-34.800956550187195,173.39300207651848</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-34.800694688009635,173.3937582563401</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-34.800330872405986,173.39451881409906</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-34.799942079237965,173.39521017664433</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-34.79946984989565,173.395786634169</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-34.79902863773037,173.39642771954934</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-34.79845878610123,173.3969285263755</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-34.801467023681866,173.38883034494776</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-34.801534297728324,173.38970956313545</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-34.801522061381775,173.39057734722562</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-34.80136711578832,173.39144968572649</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-34.8011549793645,173.3922884628015</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-34.8009509855483,173.3929992235948</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-34.80068805682884,173.3937535958179</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-34.800332022789505,173.39451967666668</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-34.799935820904466,173.3952042617922</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-34.79946966081469,173.39578639961803</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-34.79902103027725,173.39641564293095</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-34.79845153654634,173.39691546625062</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-34.80146378259313,173.38883056859413</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-34.801524109743696,173.38970980156898</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-34.80151001688296,173.39057617003826</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-34.80135895139283,173.39144868509806</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-34.80114367850718,173.3922862120677</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-34.800941019030695,173.3929941138817</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-34.80067994338384,173.39374789353295</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-34.80032397010474,173.39451363869378</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-34.79993276285502,173.3952013715807</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-34.79946915659875,173.3957857741487</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-34.79901588566796,173.39640747601038</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>-34.79844866693047,173.39691029661847</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N427"/>
+  <dimension ref="A1:N428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20922,6 +20922,54 @@
         <v>405.77</v>
       </c>
       <c r="N427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>396.81</v>
+      </c>
+      <c r="C428" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="D428" t="n">
+        <v>395.71</v>
+      </c>
+      <c r="E428" t="n">
+        <v>402.25</v>
+      </c>
+      <c r="F428" t="n">
+        <v>422.82</v>
+      </c>
+      <c r="G428" t="n">
+        <v>427.94</v>
+      </c>
+      <c r="H428" t="n">
+        <v>418.29</v>
+      </c>
+      <c r="I428" t="n">
+        <v>416.58</v>
+      </c>
+      <c r="J428" t="n">
+        <v>418.43</v>
+      </c>
+      <c r="K428" t="n">
+        <v>421.11</v>
+      </c>
+      <c r="L428" t="n">
+        <v>412.51</v>
+      </c>
+      <c r="M428" t="n">
+        <v>408.1</v>
+      </c>
+      <c r="N428" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20938,7 +20986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B501"/>
+  <dimension ref="A1:B502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25951,6 +25999,16 @@
       </c>
       <c r="B501" t="n">
         <v>-0.22</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -26119,28 +26177,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01728096325378121</v>
+        <v>-0.02131083833910224</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K2" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007288064474882949</v>
+        <v>0.001106536886671727</v>
       </c>
       <c r="M2" t="n">
-        <v>3.783209756166442</v>
+        <v>3.799740850070982</v>
       </c>
       <c r="N2" t="n">
-        <v>23.61866515467909</v>
+        <v>23.7273351650456</v>
       </c>
       <c r="O2" t="n">
-        <v>4.859903821546173</v>
+        <v>4.871071254359312</v>
       </c>
       <c r="P2" t="n">
-        <v>405.6435162661929</v>
+        <v>405.6830487622376</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26197,28 +26255,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03197687071442317</v>
+        <v>0.02770510675592491</v>
       </c>
       <c r="J3" t="n">
+        <v>427</v>
+      </c>
+      <c r="K3" t="n">
         <v>426</v>
       </c>
-      <c r="K3" t="n">
-        <v>425</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00197480151307694</v>
+        <v>0.001482343158507371</v>
       </c>
       <c r="M3" t="n">
-        <v>4.219894876002459</v>
+        <v>4.234449614139461</v>
       </c>
       <c r="N3" t="n">
-        <v>30.15450734880264</v>
+        <v>30.27143549203424</v>
       </c>
       <c r="O3" t="n">
-        <v>5.491311987931722</v>
+        <v>5.501948336001915</v>
       </c>
       <c r="P3" t="n">
-        <v>401.9146072700453</v>
+        <v>401.9560518555928</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26275,28 +26333,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05040404409291393</v>
+        <v>0.0458674640365381</v>
       </c>
       <c r="J4" t="n">
+        <v>427</v>
+      </c>
+      <c r="K4" t="n">
         <v>426</v>
       </c>
-      <c r="K4" t="n">
-        <v>425</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.003654984816690132</v>
+        <v>0.003029890394978918</v>
       </c>
       <c r="M4" t="n">
-        <v>4.947404150840043</v>
+        <v>4.960500027602816</v>
       </c>
       <c r="N4" t="n">
-        <v>40.41263802403256</v>
+        <v>40.52948097160555</v>
       </c>
       <c r="O4" t="n">
-        <v>6.357093520157822</v>
+        <v>6.366276853201214</v>
       </c>
       <c r="P4" t="n">
-        <v>403.9115790086503</v>
+        <v>403.9555928357404</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26353,28 +26411,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01698752184509155</v>
+        <v>0.01324693638467957</v>
       </c>
       <c r="J5" t="n">
+        <v>427</v>
+      </c>
+      <c r="K5" t="n">
         <v>426</v>
       </c>
-      <c r="K5" t="n">
-        <v>425</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0004001050342025136</v>
+        <v>0.0002438881615569599</v>
       </c>
       <c r="M5" t="n">
-        <v>4.956566098775682</v>
+        <v>4.964201171758964</v>
       </c>
       <c r="N5" t="n">
-        <v>42.07019282788725</v>
+        <v>42.11536934151546</v>
       </c>
       <c r="O5" t="n">
-        <v>6.486153931868041</v>
+        <v>6.48963553225568</v>
       </c>
       <c r="P5" t="n">
-        <v>409.6641889766165</v>
+        <v>409.700480076878</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26431,28 +26489,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05371411892306538</v>
+        <v>0.05082643891172327</v>
       </c>
       <c r="J6" t="n">
+        <v>427</v>
+      </c>
+      <c r="K6" t="n">
         <v>426</v>
       </c>
-      <c r="K6" t="n">
-        <v>425</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.004361545018473634</v>
+        <v>0.003920391750683372</v>
       </c>
       <c r="M6" t="n">
-        <v>4.863929067067928</v>
+        <v>4.866706359963398</v>
       </c>
       <c r="N6" t="n">
-        <v>38.43266280477985</v>
+        <v>38.42822386587009</v>
       </c>
       <c r="O6" t="n">
-        <v>6.199408262469882</v>
+        <v>6.199050239018078</v>
       </c>
       <c r="P6" t="n">
-        <v>427.4707239815837</v>
+        <v>427.4987402068308</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26509,28 +26567,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0005655593466930168</v>
+        <v>-0.003130862421838941</v>
       </c>
       <c r="J7" t="n">
+        <v>427</v>
+      </c>
+      <c r="K7" t="n">
         <v>426</v>
       </c>
-      <c r="K7" t="n">
-        <v>425</v>
-      </c>
       <c r="L7" t="n">
-        <v>4.141937536283891e-07</v>
+        <v>1.274621087554717e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.294521965019835</v>
+        <v>5.295900793410133</v>
       </c>
       <c r="N7" t="n">
-        <v>45.06246067455279</v>
+        <v>45.02437548224687</v>
       </c>
       <c r="O7" t="n">
-        <v>6.712857861935763</v>
+        <v>6.710020527706817</v>
       </c>
       <c r="P7" t="n">
-        <v>433.3433657856941</v>
+        <v>433.3682543150666</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26587,28 +26645,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03376216806224351</v>
+        <v>0.03196674119091231</v>
       </c>
       <c r="J8" t="n">
+        <v>427</v>
+      </c>
+      <c r="K8" t="n">
         <v>426</v>
       </c>
-      <c r="K8" t="n">
-        <v>425</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.001572335334793062</v>
+        <v>0.001416681079676518</v>
       </c>
       <c r="M8" t="n">
-        <v>5.155468375283181</v>
+        <v>5.15230731544616</v>
       </c>
       <c r="N8" t="n">
-        <v>42.23712477164677</v>
+        <v>42.17113671634044</v>
       </c>
       <c r="O8" t="n">
-        <v>6.499009522353908</v>
+        <v>6.493930760051299</v>
       </c>
       <c r="P8" t="n">
-        <v>421.1710415969687</v>
+        <v>421.1884607997351</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26665,28 +26723,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0455624436120507</v>
+        <v>0.04416505763010629</v>
       </c>
       <c r="J9" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K9" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003374393103692142</v>
+        <v>0.003187442197286283</v>
       </c>
       <c r="M9" t="n">
-        <v>4.790638534972449</v>
+        <v>4.786518603363223</v>
       </c>
       <c r="N9" t="n">
-        <v>35.6958887580976</v>
+        <v>35.63232438275911</v>
       </c>
       <c r="O9" t="n">
-        <v>5.974603648619514</v>
+        <v>5.969281730891843</v>
       </c>
       <c r="P9" t="n">
-        <v>418.3100576040718</v>
+        <v>418.3236283342954</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26743,28 +26801,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05440263671690847</v>
+        <v>0.05368791847263027</v>
       </c>
       <c r="J10" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K10" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00465603371822354</v>
+        <v>0.004560107747423547</v>
       </c>
       <c r="M10" t="n">
-        <v>4.935334624740664</v>
+        <v>4.927207800470939</v>
       </c>
       <c r="N10" t="n">
-        <v>36.83534873596013</v>
+        <v>36.75432378906711</v>
       </c>
       <c r="O10" t="n">
-        <v>6.069213189200074</v>
+        <v>6.062534436113919</v>
       </c>
       <c r="P10" t="n">
-        <v>418.4923276134031</v>
+        <v>418.4992686079489</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26821,28 +26879,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1535890930392694</v>
+        <v>0.1549692350024366</v>
       </c>
       <c r="J11" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K11" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03432095108734368</v>
+        <v>0.03509358002211227</v>
       </c>
       <c r="M11" t="n">
-        <v>4.983141239583077</v>
+        <v>4.978709822865091</v>
       </c>
       <c r="N11" t="n">
-        <v>38.64221948657276</v>
+        <v>38.5712636785022</v>
       </c>
       <c r="O11" t="n">
-        <v>6.216286631629268</v>
+        <v>6.210576758925229</v>
       </c>
       <c r="P11" t="n">
-        <v>414.1432971952908</v>
+        <v>414.1298939305562</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26899,28 +26957,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09426536674434768</v>
+        <v>0.09423906482212976</v>
       </c>
       <c r="J12" t="n">
+        <v>427</v>
+      </c>
+      <c r="K12" t="n">
         <v>426</v>
       </c>
-      <c r="K12" t="n">
-        <v>425</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01211759455805272</v>
+        <v>0.01217912155285605</v>
       </c>
       <c r="M12" t="n">
-        <v>5.253427831140098</v>
+        <v>5.241212550704515</v>
       </c>
       <c r="N12" t="n">
-        <v>42.0124092656825</v>
+        <v>41.91379564699745</v>
       </c>
       <c r="O12" t="n">
-        <v>6.481698023333276</v>
+        <v>6.474086472004946</v>
       </c>
       <c r="P12" t="n">
-        <v>410.071249740818</v>
+        <v>410.0715061221117</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26977,28 +27035,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.308728777497979</v>
+        <v>0.309193908241169</v>
       </c>
       <c r="J13" t="n">
+        <v>427</v>
+      </c>
+      <c r="K13" t="n">
         <v>426</v>
       </c>
-      <c r="K13" t="n">
-        <v>425</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09105502918686625</v>
+        <v>0.09177471839293905</v>
       </c>
       <c r="M13" t="n">
-        <v>5.962967312340115</v>
+        <v>5.951183168209942</v>
       </c>
       <c r="N13" t="n">
-        <v>55.04478812015495</v>
+        <v>54.91777424701071</v>
       </c>
       <c r="O13" t="n">
-        <v>7.419217487050433</v>
+        <v>7.410652754448201</v>
       </c>
       <c r="P13" t="n">
-        <v>398.9505666420069</v>
+        <v>398.946025775017</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27036,7 +27094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N427"/>
+  <dimension ref="A1:N428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57735,6 +57793,78 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-34.801443615818755,173.3888319601711</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-34.80151401191823,173.38971003789246</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-34.80148619753818,173.39057384201956</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-34.801325396624314,173.3914445726273</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-34.80110416999763,173.39227834336546</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-34.80090530567401,173.39297580408663</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-34.800642496710935,173.39372157530923</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-34.80030134589342,173.39449667487148</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-34.79991028974537,173.39518013189337</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-34.79945037455278,173.39576247542172</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-34.7989934464082,173.39637185434748</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-34.79843693674396,173.39688916461716</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N428"/>
+  <dimension ref="A1:N429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20972,6 +20972,54 @@
       <c r="N428" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>398.06</v>
+      </c>
+      <c r="C429" t="n">
+        <v>395.47</v>
+      </c>
+      <c r="D429" t="n">
+        <v>397.26</v>
+      </c>
+      <c r="E429" t="n">
+        <v>404.57</v>
+      </c>
+      <c r="F429" t="n">
+        <v>424.76</v>
+      </c>
+      <c r="G429" t="n">
+        <v>429.42</v>
+      </c>
+      <c r="H429" t="n">
+        <v>420.24</v>
+      </c>
+      <c r="I429" t="n">
+        <v>417.81</v>
+      </c>
+      <c r="J429" t="n">
+        <v>419.92</v>
+      </c>
+      <c r="K429" t="n">
+        <v>422.07</v>
+      </c>
+      <c r="L429" t="n">
+        <v>413.83</v>
+      </c>
+      <c r="M429" t="n">
+        <v>409.6</v>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20986,7 +21034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26009,6 +26057,16 @@
       </c>
       <c r="B502" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -26177,28 +26235,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02131083833910224</v>
+        <v>-0.02468529203149757</v>
       </c>
       <c r="J2" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K2" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001106536886671727</v>
+        <v>0.001485258780617893</v>
       </c>
       <c r="M2" t="n">
-        <v>3.799740850070982</v>
+        <v>3.812026236949666</v>
       </c>
       <c r="N2" t="n">
-        <v>23.7273351650456</v>
+        <v>23.78788148515726</v>
       </c>
       <c r="O2" t="n">
-        <v>4.871071254359312</v>
+        <v>4.877282182236051</v>
       </c>
       <c r="P2" t="n">
-        <v>405.6830487622376</v>
+        <v>405.7161824409881</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26255,28 +26313,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02770510675592491</v>
+        <v>0.02428999378355172</v>
       </c>
       <c r="J3" t="n">
+        <v>428</v>
+      </c>
+      <c r="K3" t="n">
         <v>427</v>
       </c>
-      <c r="K3" t="n">
-        <v>426</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.001482343158507371</v>
+        <v>0.00114167203309179</v>
       </c>
       <c r="M3" t="n">
-        <v>4.234449614139461</v>
+        <v>4.244464663440828</v>
       </c>
       <c r="N3" t="n">
-        <v>30.27143549203424</v>
+        <v>30.32171998186181</v>
       </c>
       <c r="O3" t="n">
-        <v>5.501948336001915</v>
+        <v>5.506516138345716</v>
       </c>
       <c r="P3" t="n">
-        <v>401.9560518555928</v>
+        <v>401.9892162693054</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26333,28 +26391,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0458674640365381</v>
+        <v>0.04212598523953929</v>
       </c>
       <c r="J4" t="n">
+        <v>428</v>
+      </c>
+      <c r="K4" t="n">
         <v>427</v>
       </c>
-      <c r="K4" t="n">
-        <v>426</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.003029890394978918</v>
+        <v>0.002562184043947591</v>
       </c>
       <c r="M4" t="n">
-        <v>4.960500027602816</v>
+        <v>4.969176894957803</v>
       </c>
       <c r="N4" t="n">
-        <v>40.52948097160555</v>
+        <v>40.58000936469642</v>
       </c>
       <c r="O4" t="n">
-        <v>6.366276853201214</v>
+        <v>6.370244058487589</v>
       </c>
       <c r="P4" t="n">
-        <v>403.9555928357404</v>
+        <v>403.9919266120239</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26411,28 +26469,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01324693638467957</v>
+        <v>0.01065523431482698</v>
       </c>
       <c r="J5" t="n">
+        <v>428</v>
+      </c>
+      <c r="K5" t="n">
         <v>427</v>
       </c>
-      <c r="K5" t="n">
-        <v>426</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0002438881615569599</v>
+        <v>0.0001584348079469722</v>
       </c>
       <c r="M5" t="n">
-        <v>4.964201171758964</v>
+        <v>4.966048970488847</v>
       </c>
       <c r="N5" t="n">
-        <v>42.11536934151546</v>
+        <v>42.08652686088615</v>
       </c>
       <c r="O5" t="n">
-        <v>6.48963553225568</v>
+        <v>6.487412955939074</v>
       </c>
       <c r="P5" t="n">
-        <v>409.700480076878</v>
+        <v>409.7256482866443</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26489,28 +26547,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05082643891172327</v>
+        <v>0.04889228149669128</v>
       </c>
       <c r="J6" t="n">
+        <v>428</v>
+      </c>
+      <c r="K6" t="n">
         <v>427</v>
       </c>
-      <c r="K6" t="n">
-        <v>426</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.003920391750683372</v>
+        <v>0.003645514812145367</v>
       </c>
       <c r="M6" t="n">
-        <v>4.866706359963398</v>
+        <v>4.864971743576262</v>
       </c>
       <c r="N6" t="n">
-        <v>38.42822386587009</v>
+        <v>38.37709640913904</v>
       </c>
       <c r="O6" t="n">
-        <v>6.199050239018078</v>
+        <v>6.19492505274592</v>
       </c>
       <c r="P6" t="n">
-        <v>427.4987402068308</v>
+        <v>427.517522952004</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26567,28 +26625,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.003130862421838941</v>
+        <v>-0.004960515048435636</v>
       </c>
       <c r="J7" t="n">
+        <v>428</v>
+      </c>
+      <c r="K7" t="n">
         <v>427</v>
       </c>
-      <c r="K7" t="n">
-        <v>426</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.274621087554717e-05</v>
+        <v>3.215218541230414e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.295900793410133</v>
+        <v>5.293377876640768</v>
       </c>
       <c r="N7" t="n">
-        <v>45.02437548224687</v>
+        <v>44.95371362623249</v>
       </c>
       <c r="O7" t="n">
-        <v>6.710020527706817</v>
+        <v>6.704753062285925</v>
       </c>
       <c r="P7" t="n">
-        <v>433.3682543150666</v>
+        <v>433.3860222065389</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26645,28 +26703,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03196674119091231</v>
+        <v>0.03111634362002622</v>
       </c>
       <c r="J8" t="n">
+        <v>428</v>
+      </c>
+      <c r="K8" t="n">
         <v>427</v>
       </c>
-      <c r="K8" t="n">
-        <v>426</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.001416681079676518</v>
+        <v>0.001349747218350905</v>
       </c>
       <c r="M8" t="n">
-        <v>5.15230731544616</v>
+        <v>5.144458363933682</v>
       </c>
       <c r="N8" t="n">
-        <v>42.17113671634044</v>
+        <v>42.07988902425875</v>
       </c>
       <c r="O8" t="n">
-        <v>6.493930760051299</v>
+        <v>6.486901342263404</v>
       </c>
       <c r="P8" t="n">
-        <v>421.1884607997351</v>
+        <v>421.1967190732063</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26723,28 +26781,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04416505763010629</v>
+        <v>0.04336713267231029</v>
       </c>
       <c r="J9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003187442197286283</v>
+        <v>0.003090418413262519</v>
       </c>
       <c r="M9" t="n">
-        <v>4.786518603363223</v>
+        <v>4.779372370882045</v>
       </c>
       <c r="N9" t="n">
-        <v>35.63232438275911</v>
+        <v>35.55566849228412</v>
       </c>
       <c r="O9" t="n">
-        <v>5.969281730891843</v>
+        <v>5.962857410024503</v>
       </c>
       <c r="P9" t="n">
-        <v>418.3236283342954</v>
+        <v>418.3313846245928</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26801,28 +26859,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05368791847263027</v>
+        <v>0.05368493739410578</v>
       </c>
       <c r="J10" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K10" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004560107747423547</v>
+        <v>0.004585274738307499</v>
       </c>
       <c r="M10" t="n">
-        <v>4.927207800470939</v>
+        <v>4.915709927410348</v>
       </c>
       <c r="N10" t="n">
-        <v>36.75432378906711</v>
+        <v>36.66844929285858</v>
       </c>
       <c r="O10" t="n">
-        <v>6.062534436113919</v>
+        <v>6.055447901919277</v>
       </c>
       <c r="P10" t="n">
-        <v>418.4992686079489</v>
+        <v>418.4992975857496</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26879,28 +26937,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1549692350024366</v>
+        <v>0.1567813819613134</v>
       </c>
       <c r="J11" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K11" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03509358002211227</v>
+        <v>0.03605442756738686</v>
       </c>
       <c r="M11" t="n">
-        <v>4.978709822865091</v>
+        <v>4.976542294405514</v>
       </c>
       <c r="N11" t="n">
-        <v>38.5712636785022</v>
+        <v>38.51517082323925</v>
       </c>
       <c r="O11" t="n">
-        <v>6.210576758925229</v>
+        <v>6.206059202363384</v>
       </c>
       <c r="P11" t="n">
-        <v>414.1298939305562</v>
+        <v>414.1122788180855</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26957,28 +27015,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09423906482212976</v>
+        <v>0.09483622658031846</v>
       </c>
       <c r="J12" t="n">
+        <v>428</v>
+      </c>
+      <c r="K12" t="n">
         <v>427</v>
       </c>
-      <c r="K12" t="n">
-        <v>426</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01217912155285605</v>
+        <v>0.01239995023716467</v>
       </c>
       <c r="M12" t="n">
-        <v>5.241212550704515</v>
+        <v>5.232144296058499</v>
       </c>
       <c r="N12" t="n">
-        <v>41.91379564699745</v>
+        <v>41.81931284434631</v>
       </c>
       <c r="O12" t="n">
-        <v>6.474086472004946</v>
+        <v>6.46678535629151</v>
       </c>
       <c r="P12" t="n">
-        <v>410.0715061221117</v>
+        <v>410.0656797941921</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27035,28 +27093,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.309193908241169</v>
+        <v>0.3103625698933101</v>
       </c>
       <c r="J13" t="n">
+        <v>428</v>
+      </c>
+      <c r="K13" t="n">
         <v>427</v>
       </c>
-      <c r="K13" t="n">
-        <v>426</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09177471839293905</v>
+        <v>0.09285946347260143</v>
       </c>
       <c r="M13" t="n">
-        <v>5.951183168209942</v>
+        <v>5.942783729211786</v>
       </c>
       <c r="N13" t="n">
-        <v>54.91777424701071</v>
+        <v>54.80318432543928</v>
       </c>
       <c r="O13" t="n">
-        <v>7.410652754448201</v>
+        <v>7.402917284789779</v>
       </c>
       <c r="P13" t="n">
-        <v>398.946025775017</v>
+        <v>398.9346060570487</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27094,7 +27152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N428"/>
+  <dimension ref="A1:N429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57865,6 +57923,78 @@
         </is>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-34.80143236203836,173.3888327367205</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-34.801498775020825,173.3897103944876</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-34.801472265468504,173.3905724803489</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-34.801304581901434,173.3914420215777</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-34.80108690727022,173.3922749052412</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-34.800893013634244,173.39296950211434</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-34.80062728399833,173.39371088353764</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-34.80029191274695,173.3944896018229</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-34.79989969324612,173.39517011698155</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-34.7994443239598,173.3957549697938</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-34.79898622205888,173.39636038591377</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-34.798429385119775,173.39687556032763</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N429"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21020,6 +21020,54 @@
       <c r="N429" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>398.79</v>
+      </c>
+      <c r="C430" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="D430" t="n">
+        <v>396.43</v>
+      </c>
+      <c r="E430" t="n">
+        <v>404.62</v>
+      </c>
+      <c r="F430" t="n">
+        <v>425.41</v>
+      </c>
+      <c r="G430" t="n">
+        <v>429.37</v>
+      </c>
+      <c r="H430" t="n">
+        <v>419.95</v>
+      </c>
+      <c r="I430" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="J430" t="n">
+        <v>419.75</v>
+      </c>
+      <c r="K430" t="n">
+        <v>417.74</v>
+      </c>
+      <c r="L430" t="n">
+        <v>413.33</v>
+      </c>
+      <c r="M430" t="n">
+        <v>408.44</v>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B503"/>
+  <dimension ref="A1:B504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26067,6 +26115,16 @@
       </c>
       <c r="B503" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -26235,28 +26293,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02468529203149757</v>
+        <v>-0.02769909399860883</v>
       </c>
       <c r="J2" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K2" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001485258780617893</v>
+        <v>0.001872867895711505</v>
       </c>
       <c r="M2" t="n">
-        <v>3.812026236949666</v>
+        <v>3.821787506046992</v>
       </c>
       <c r="N2" t="n">
-        <v>23.78788148515726</v>
+        <v>23.82372537934331</v>
       </c>
       <c r="O2" t="n">
-        <v>4.877282182236051</v>
+        <v>4.880955375676294</v>
       </c>
       <c r="P2" t="n">
-        <v>405.7161824409881</v>
+        <v>405.7459659752568</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26313,28 +26371,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02428999378355172</v>
+        <v>0.02099595231267096</v>
       </c>
       <c r="J3" t="n">
+        <v>429</v>
+      </c>
+      <c r="K3" t="n">
         <v>428</v>
       </c>
-      <c r="K3" t="n">
-        <v>427</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00114167203309179</v>
+        <v>0.0008550120481664036</v>
       </c>
       <c r="M3" t="n">
-        <v>4.244464663440828</v>
+        <v>4.253766648467723</v>
       </c>
       <c r="N3" t="n">
-        <v>30.32171998186181</v>
+        <v>30.36227039063039</v>
       </c>
       <c r="O3" t="n">
-        <v>5.506516138345716</v>
+        <v>5.510196946628168</v>
       </c>
       <c r="P3" t="n">
-        <v>401.9892162693054</v>
+        <v>402.0214131407342</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26391,28 +26449,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04212598523953929</v>
+        <v>0.03799744950847411</v>
       </c>
       <c r="J4" t="n">
+        <v>429</v>
+      </c>
+      <c r="K4" t="n">
         <v>428</v>
       </c>
-      <c r="K4" t="n">
-        <v>427</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.002562184043947591</v>
+        <v>0.002088518883613055</v>
       </c>
       <c r="M4" t="n">
-        <v>4.969176894957803</v>
+        <v>4.979623625460592</v>
       </c>
       <c r="N4" t="n">
-        <v>40.58000936469642</v>
+        <v>40.66018165609122</v>
       </c>
       <c r="O4" t="n">
-        <v>6.370244058487589</v>
+        <v>6.376533670897631</v>
       </c>
       <c r="P4" t="n">
-        <v>403.9919266120239</v>
+        <v>404.0322800609094</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26469,28 +26527,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01065523431482698</v>
+        <v>0.008093215574297796</v>
       </c>
       <c r="J5" t="n">
+        <v>429</v>
+      </c>
+      <c r="K5" t="n">
         <v>428</v>
       </c>
-      <c r="K5" t="n">
-        <v>427</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0001584348079469722</v>
+        <v>9.178791993302848e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.966048970488847</v>
+        <v>4.967668267494911</v>
       </c>
       <c r="N5" t="n">
-        <v>42.08652686088615</v>
+        <v>42.0555805740966</v>
       </c>
       <c r="O5" t="n">
-        <v>6.487412955939074</v>
+        <v>6.485027415061297</v>
       </c>
       <c r="P5" t="n">
-        <v>409.7256482866443</v>
+        <v>409.7506901656601</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26547,28 +26605,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04889228149669128</v>
+        <v>0.04727222744555447</v>
       </c>
       <c r="J6" t="n">
+        <v>429</v>
+      </c>
+      <c r="K6" t="n">
         <v>428</v>
       </c>
-      <c r="K6" t="n">
-        <v>427</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.003645514812145367</v>
+        <v>0.00342583800088847</v>
       </c>
       <c r="M6" t="n">
-        <v>4.864971743576262</v>
+        <v>4.861759276653267</v>
       </c>
       <c r="N6" t="n">
-        <v>38.37709640913904</v>
+        <v>38.3143747087356</v>
       </c>
       <c r="O6" t="n">
-        <v>6.19492505274592</v>
+        <v>6.189860637262814</v>
       </c>
       <c r="P6" t="n">
-        <v>427.517522952004</v>
+        <v>427.5333578078954</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26625,28 +26683,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.004960515048435636</v>
+        <v>-0.00680628806749068</v>
       </c>
       <c r="J7" t="n">
+        <v>429</v>
+      </c>
+      <c r="K7" t="n">
         <v>428</v>
       </c>
-      <c r="K7" t="n">
-        <v>427</v>
-      </c>
       <c r="L7" t="n">
-        <v>3.215218541230414e-05</v>
+        <v>6.082929801043413e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.293377876640768</v>
+        <v>5.290986173982275</v>
       </c>
       <c r="N7" t="n">
-        <v>44.95371362623249</v>
+        <v>44.88365727573478</v>
       </c>
       <c r="O7" t="n">
-        <v>6.704753062285925</v>
+        <v>6.699526645647047</v>
       </c>
       <c r="P7" t="n">
-        <v>433.3860222065389</v>
+        <v>433.4040633019854</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26703,28 +26761,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03111634362002622</v>
+        <v>0.03012765712927471</v>
       </c>
       <c r="J8" t="n">
+        <v>429</v>
+      </c>
+      <c r="K8" t="n">
         <v>428</v>
       </c>
-      <c r="K8" t="n">
-        <v>427</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.001349747218350905</v>
+        <v>0.001272395399223303</v>
       </c>
       <c r="M8" t="n">
-        <v>5.144458363933682</v>
+        <v>5.137268978434012</v>
       </c>
       <c r="N8" t="n">
-        <v>42.07988902425875</v>
+        <v>41.99160674688855</v>
       </c>
       <c r="O8" t="n">
-        <v>6.486901342263404</v>
+        <v>6.480093112516868</v>
       </c>
       <c r="P8" t="n">
-        <v>421.1967190732063</v>
+        <v>421.2063827681256</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26781,28 +26839,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04336713267231029</v>
+        <v>0.04256574548435276</v>
       </c>
       <c r="J9" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K9" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003090418413262519</v>
+        <v>0.002994091832346335</v>
       </c>
       <c r="M9" t="n">
-        <v>4.779372370882045</v>
+        <v>4.772227245796164</v>
       </c>
       <c r="N9" t="n">
-        <v>35.55566849228412</v>
+        <v>35.47936351362812</v>
       </c>
       <c r="O9" t="n">
-        <v>5.962857410024503</v>
+        <v>5.956455616692542</v>
       </c>
       <c r="P9" t="n">
-        <v>418.3313846245928</v>
+        <v>418.3392250791426</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26859,28 +26917,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05368493739410578</v>
+        <v>0.05359964139101982</v>
       </c>
       <c r="J10" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K10" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004585274738307499</v>
+        <v>0.004596905400078954</v>
       </c>
       <c r="M10" t="n">
-        <v>4.915709927410348</v>
+        <v>4.904654336411272</v>
       </c>
       <c r="N10" t="n">
-        <v>36.66844929285858</v>
+        <v>36.58304954116113</v>
       </c>
       <c r="O10" t="n">
-        <v>6.055447901919277</v>
+        <v>6.04839231045417</v>
       </c>
       <c r="P10" t="n">
-        <v>418.4992975857496</v>
+        <v>418.5001320880297</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26937,28 +26995,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1567813819613134</v>
+        <v>0.1565191348493377</v>
       </c>
       <c r="J11" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K11" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03605442756738686</v>
+        <v>0.03613656245419516</v>
       </c>
       <c r="M11" t="n">
-        <v>4.976542294405514</v>
+        <v>4.966144827162426</v>
       </c>
       <c r="N11" t="n">
-        <v>38.51517082323925</v>
+        <v>38.42609600646433</v>
       </c>
       <c r="O11" t="n">
-        <v>6.206059202363384</v>
+        <v>6.198878608785973</v>
       </c>
       <c r="P11" t="n">
-        <v>414.1122788180855</v>
+        <v>414.1148445398654</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27015,28 +27073,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09483622658031846</v>
+        <v>0.09518651284582459</v>
       </c>
       <c r="J12" t="n">
+        <v>429</v>
+      </c>
+      <c r="K12" t="n">
         <v>428</v>
       </c>
-      <c r="K12" t="n">
-        <v>427</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01239995023716467</v>
+        <v>0.01256113810951109</v>
       </c>
       <c r="M12" t="n">
-        <v>5.232144296058499</v>
+        <v>5.221772663841097</v>
       </c>
       <c r="N12" t="n">
-        <v>41.81931284434631</v>
+        <v>41.72285389653414</v>
       </c>
       <c r="O12" t="n">
-        <v>6.46678535629151</v>
+        <v>6.459323021535162</v>
       </c>
       <c r="P12" t="n">
-        <v>410.0656797941921</v>
+        <v>410.0622400561978</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27093,28 +27151,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3103625698933101</v>
+        <v>0.3109460041643739</v>
       </c>
       <c r="J13" t="n">
+        <v>429</v>
+      </c>
+      <c r="K13" t="n">
         <v>428</v>
       </c>
-      <c r="K13" t="n">
-        <v>427</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09285946347260143</v>
+        <v>0.09365744660395614</v>
       </c>
       <c r="M13" t="n">
-        <v>5.942783729211786</v>
+        <v>5.931620310527911</v>
       </c>
       <c r="N13" t="n">
-        <v>54.80318432543928</v>
+        <v>54.67859280898499</v>
       </c>
       <c r="O13" t="n">
-        <v>7.402917284789779</v>
+        <v>7.394497468319601</v>
       </c>
       <c r="P13" t="n">
-        <v>398.9346060570487</v>
+        <v>398.928868205873</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27152,7 +27210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N429"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57995,6 +58053,78 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-34.80142578983061,173.38883319022526</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-34.80149670136023,173.38971044301826</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-34.80147972586711,173.39057320950153</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-34.801304133308264,173.3914419665982</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-34.801081123366686,173.3922737532927</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-34.80089342890587,173.39296971501875</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-34.80062954640181,173.39371247359574</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-34.800291989439195,173.39448965932735</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-34.799900902242726,173.39517125962237</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-34.7994716146514,173.39578882331173</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-34.79898895855497,173.39636473001718</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-34.79843522504262,173.39688608097796</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N430"/>
+  <dimension ref="A1:N432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21068,6 +21068,102 @@
       <c r="N430" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>399.26</v>
+      </c>
+      <c r="C431" t="n">
+        <v>396.43</v>
+      </c>
+      <c r="D431" t="n">
+        <v>397.02</v>
+      </c>
+      <c r="E431" t="n">
+        <v>404.61</v>
+      </c>
+      <c r="F431" t="n">
+        <v>425.49</v>
+      </c>
+      <c r="G431" t="n">
+        <v>429.83</v>
+      </c>
+      <c r="H431" t="n">
+        <v>420.77</v>
+      </c>
+      <c r="I431" t="n">
+        <v>418.55</v>
+      </c>
+      <c r="J431" t="n">
+        <v>420.21</v>
+      </c>
+      <c r="K431" t="n">
+        <v>418.41</v>
+      </c>
+      <c r="L431" t="n">
+        <v>414.01</v>
+      </c>
+      <c r="M431" t="n">
+        <v>409.26</v>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>401.08</v>
+      </c>
+      <c r="C432" t="n">
+        <v>398.06</v>
+      </c>
+      <c r="D432" t="n">
+        <v>399.14</v>
+      </c>
+      <c r="E432" t="n">
+        <v>406.51</v>
+      </c>
+      <c r="F432" t="n">
+        <v>426.26</v>
+      </c>
+      <c r="G432" t="n">
+        <v>432.12</v>
+      </c>
+      <c r="H432" t="n">
+        <v>422.94</v>
+      </c>
+      <c r="I432" t="n">
+        <v>419.58</v>
+      </c>
+      <c r="J432" t="n">
+        <v>421.93</v>
+      </c>
+      <c r="K432" t="n">
+        <v>420.39</v>
+      </c>
+      <c r="L432" t="n">
+        <v>416.52</v>
+      </c>
+      <c r="M432" t="n">
+        <v>411.33</v>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21082,7 +21178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B504"/>
+  <dimension ref="A1:B507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26125,6 +26221,36 @@
       </c>
       <c r="B504" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -26293,28 +26419,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02769909399860883</v>
+        <v>-0.0322841325627409</v>
       </c>
       <c r="J2" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001872867895711505</v>
+        <v>0.002559581317832738</v>
       </c>
       <c r="M2" t="n">
-        <v>3.821787506046992</v>
+        <v>3.832371756267004</v>
       </c>
       <c r="N2" t="n">
-        <v>23.82372537934331</v>
+        <v>23.82363778363754</v>
       </c>
       <c r="O2" t="n">
-        <v>4.880955375676294</v>
+        <v>4.880946402454911</v>
       </c>
       <c r="P2" t="n">
-        <v>405.7459659752568</v>
+        <v>405.791351573975</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26371,28 +26497,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02099595231267096</v>
+        <v>0.01598527493688729</v>
       </c>
       <c r="J3" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K3" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008550120481664036</v>
+        <v>0.000499242494784613</v>
       </c>
       <c r="M3" t="n">
-        <v>4.253766648467723</v>
+        <v>4.262987912748774</v>
       </c>
       <c r="N3" t="n">
-        <v>30.36227039063039</v>
+        <v>30.35466969070103</v>
       </c>
       <c r="O3" t="n">
-        <v>5.510196946628168</v>
+        <v>5.509507209424545</v>
       </c>
       <c r="P3" t="n">
-        <v>402.0214131407342</v>
+        <v>402.0704716648093</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26449,28 +26575,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03799744950847411</v>
+        <v>0.03146039014710923</v>
       </c>
       <c r="J4" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K4" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002088518883613055</v>
+        <v>0.001440915075726745</v>
       </c>
       <c r="M4" t="n">
-        <v>4.979623625460592</v>
+        <v>4.991117727223042</v>
       </c>
       <c r="N4" t="n">
-        <v>40.66018165609122</v>
+        <v>40.69839647016445</v>
       </c>
       <c r="O4" t="n">
-        <v>6.376533670897631</v>
+        <v>6.379529486581628</v>
       </c>
       <c r="P4" t="n">
-        <v>404.0322800609094</v>
+        <v>404.0962831613425</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26527,28 +26653,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008093215574297796</v>
+        <v>0.003959428916736707</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K5" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L5" t="n">
-        <v>9.178791993302848e-05</v>
+        <v>2.217203341736695e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.967668267494911</v>
+        <v>4.965883207921757</v>
       </c>
       <c r="N5" t="n">
-        <v>42.0555805740966</v>
+        <v>41.95306116790392</v>
       </c>
       <c r="O5" t="n">
-        <v>6.485027415061297</v>
+        <v>6.477118276510312</v>
       </c>
       <c r="P5" t="n">
-        <v>409.7506901656601</v>
+        <v>409.7911608435923</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26605,28 +26731,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04727222744555447</v>
+        <v>0.04452979501970039</v>
       </c>
       <c r="J6" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K6" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00342583800088847</v>
+        <v>0.003072478096281306</v>
       </c>
       <c r="M6" t="n">
-        <v>4.861759276653267</v>
+        <v>4.852911501090963</v>
       </c>
       <c r="N6" t="n">
-        <v>38.3143747087356</v>
+        <v>38.17595324525428</v>
       </c>
       <c r="O6" t="n">
-        <v>6.189860637262814</v>
+        <v>6.178669213127878</v>
       </c>
       <c r="P6" t="n">
-        <v>427.5333578078954</v>
+        <v>427.5602089312248</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26683,28 +26809,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.00680628806749068</v>
+        <v>-0.008913709964115628</v>
       </c>
       <c r="J7" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K7" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L7" t="n">
-        <v>6.082929801043413e-05</v>
+        <v>0.0001054478692269489</v>
       </c>
       <c r="M7" t="n">
-        <v>5.290986173982275</v>
+        <v>5.277684787719161</v>
       </c>
       <c r="N7" t="n">
-        <v>44.88365727573478</v>
+        <v>44.70407359421188</v>
       </c>
       <c r="O7" t="n">
-        <v>6.699526645647047</v>
+        <v>6.686110498205357</v>
       </c>
       <c r="P7" t="n">
-        <v>433.4040633019854</v>
+        <v>433.4246898511822</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26761,28 +26887,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03012765712927471</v>
+        <v>0.02998494967567783</v>
       </c>
       <c r="J8" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K8" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001272395399223303</v>
+        <v>0.001274590385514807</v>
       </c>
       <c r="M8" t="n">
-        <v>5.137268978434012</v>
+        <v>5.118416277967114</v>
       </c>
       <c r="N8" t="n">
-        <v>41.99160674688855</v>
+        <v>41.80188034192065</v>
       </c>
       <c r="O8" t="n">
-        <v>6.480093112516868</v>
+        <v>6.465437366638134</v>
       </c>
       <c r="P8" t="n">
-        <v>421.2063827681256</v>
+        <v>421.207770954923</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26839,28 +26965,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04256574548435276</v>
+        <v>0.04218036392378853</v>
       </c>
       <c r="J9" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K9" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002994091832346335</v>
+        <v>0.002973604322093815</v>
       </c>
       <c r="M9" t="n">
-        <v>4.772227245796164</v>
+        <v>4.752516617173779</v>
       </c>
       <c r="N9" t="n">
-        <v>35.47936351362812</v>
+        <v>35.31674384610425</v>
       </c>
       <c r="O9" t="n">
-        <v>5.956455616692542</v>
+        <v>5.942789231169506</v>
       </c>
       <c r="P9" t="n">
-        <v>418.3392250791426</v>
+        <v>418.3429979863332</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26917,28 +27043,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05359964139101982</v>
+        <v>0.05466950565771475</v>
       </c>
       <c r="J10" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K10" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004596905400078954</v>
+        <v>0.00483449271337022</v>
       </c>
       <c r="M10" t="n">
-        <v>4.904654336411272</v>
+        <v>4.88731303129856</v>
       </c>
       <c r="N10" t="n">
-        <v>36.58304954116113</v>
+        <v>36.42262414891184</v>
       </c>
       <c r="O10" t="n">
-        <v>6.04839231045417</v>
+        <v>6.035115918432043</v>
       </c>
       <c r="P10" t="n">
-        <v>418.5001320880297</v>
+        <v>418.4896385719226</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26995,28 +27121,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1565191348493377</v>
+        <v>0.1575557662780527</v>
       </c>
       <c r="J11" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K11" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03613656245419516</v>
+        <v>0.03699251702986028</v>
       </c>
       <c r="M11" t="n">
-        <v>4.966144827162426</v>
+        <v>4.94846118283805</v>
       </c>
       <c r="N11" t="n">
-        <v>38.42609600646433</v>
+        <v>38.25788149844205</v>
       </c>
       <c r="O11" t="n">
-        <v>6.198878608785973</v>
+        <v>6.18529558699033</v>
       </c>
       <c r="P11" t="n">
-        <v>414.1148445398654</v>
+        <v>414.1046756380225</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27073,28 +27199,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09518651284582459</v>
+        <v>0.09769189258642867</v>
       </c>
       <c r="J12" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K12" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01256113810951109</v>
+        <v>0.01335889156525794</v>
       </c>
       <c r="M12" t="n">
-        <v>5.221772663841097</v>
+        <v>5.21067694903391</v>
       </c>
       <c r="N12" t="n">
-        <v>41.72285389653414</v>
+        <v>41.56841576065642</v>
       </c>
       <c r="O12" t="n">
-        <v>6.459323021535162</v>
+        <v>6.447357269506353</v>
       </c>
       <c r="P12" t="n">
-        <v>410.0622400561978</v>
+        <v>410.037582270372</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27151,28 +27277,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3109460041643739</v>
+        <v>0.3138315611207697</v>
       </c>
       <c r="J13" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K13" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09365744660395614</v>
+        <v>0.09614769310607174</v>
       </c>
       <c r="M13" t="n">
-        <v>5.931620310527911</v>
+        <v>5.917369541579832</v>
       </c>
       <c r="N13" t="n">
-        <v>54.67859280898499</v>
+        <v>54.47188876571641</v>
       </c>
       <c r="O13" t="n">
-        <v>7.394497468319601</v>
+        <v>7.380507351511576</v>
       </c>
       <c r="P13" t="n">
-        <v>398.928868205873</v>
+        <v>398.9004295983269</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27210,7 +27336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N430"/>
+  <dimension ref="A1:N432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58125,6 +58251,150 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-34.80142155840919,173.3888334822077</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-34.8014901197418,173.38971059705048</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-34.8014744226922,173.3905726911882</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-34.80130422302689,173.3914419775941</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-34.80108041150163,173.39227361151444</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-34.80088960840695,173.39296775629802</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-34.800623149260886,173.39370797756968</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-34.80028623752041,173.39448534649364</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-34.79989763084013,173.3951681677708</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-34.799467391842946,173.39578358500611</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-34.79898523692025,173.39635882203658</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-34.79843109682139,173.39687864396637</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-34.801405172904865,173.38883461286298</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-34.801475423799296,173.38971094098525</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-34.80145536721622,173.3905708287748</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-34.8012871764865,173.39143988837344</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-34.80107355980047,173.39227224689876</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-34.80087058896619,173.39295800527782</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-34.80060622024077,173.3936960795528</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-34.800278338218334,173.39447942353632</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-34.79988539863839,173.39515660693675</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-34.79945491249718,173.39576810464337</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-34.79897149970724,173.3963370146421</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-34.798420675577944,173.3968598700501</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0019/nzd0019.xlsx
+++ b/data/nzd0019/nzd0019.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N432"/>
+  <dimension ref="A1:N434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21164,6 +21164,102 @@
       <c r="N432" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>400.94</v>
+      </c>
+      <c r="C433" t="n">
+        <v>400.27</v>
+      </c>
+      <c r="D433" t="n">
+        <v>400.42</v>
+      </c>
+      <c r="E433" t="n">
+        <v>406.52</v>
+      </c>
+      <c r="F433" t="n">
+        <v>426.5</v>
+      </c>
+      <c r="G433" t="n">
+        <v>431.62</v>
+      </c>
+      <c r="H433" t="n">
+        <v>422.25</v>
+      </c>
+      <c r="I433" t="n">
+        <v>419.62</v>
+      </c>
+      <c r="J433" t="n">
+        <v>421.14</v>
+      </c>
+      <c r="K433" t="n">
+        <v>420.34</v>
+      </c>
+      <c r="L433" t="n">
+        <v>415.52</v>
+      </c>
+      <c r="M433" t="n">
+        <v>410.22</v>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>401.65</v>
+      </c>
+      <c r="C434" t="n">
+        <v>400.14</v>
+      </c>
+      <c r="D434" t="n">
+        <v>400.12</v>
+      </c>
+      <c r="E434" t="n">
+        <v>406.63</v>
+      </c>
+      <c r="F434" t="n">
+        <v>426.67</v>
+      </c>
+      <c r="G434" t="n">
+        <v>431.75</v>
+      </c>
+      <c r="H434" t="n">
+        <v>421.84</v>
+      </c>
+      <c r="I434" t="n">
+        <v>419.28</v>
+      </c>
+      <c r="J434" t="n">
+        <v>421.04</v>
+      </c>
+      <c r="K434" t="n">
+        <v>420.34</v>
+      </c>
+      <c r="L434" t="n">
+        <v>415.42</v>
+      </c>
+      <c r="M434" t="n">
+        <v>410.14</v>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21178,7 +21274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B507"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26251,6 +26347,26 @@
       </c>
       <c r="B507" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -26419,28 +26535,28 @@
         <v>0.0679</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0322841325627409</v>
+        <v>-0.03570626150073358</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K2" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002559581317832738</v>
+        <v>0.003156690085368119</v>
       </c>
       <c r="M2" t="n">
-        <v>3.832371756267004</v>
+        <v>3.835796925328205</v>
       </c>
       <c r="N2" t="n">
-        <v>23.82363778363754</v>
+        <v>23.7737252155138</v>
       </c>
       <c r="O2" t="n">
-        <v>4.880946402454911</v>
+        <v>4.875830720555606</v>
       </c>
       <c r="P2" t="n">
-        <v>405.791351573975</v>
+        <v>405.8253709071818</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26497,28 +26613,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01598527493688729</v>
+        <v>0.01384829833743078</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K3" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000499242494784613</v>
+        <v>0.0003786897024080638</v>
       </c>
       <c r="M3" t="n">
-        <v>4.262987912748774</v>
+        <v>4.255464267576775</v>
       </c>
       <c r="N3" t="n">
-        <v>30.35466969070103</v>
+        <v>30.23814013595671</v>
       </c>
       <c r="O3" t="n">
-        <v>5.509507209424545</v>
+        <v>5.498921724843581</v>
       </c>
       <c r="P3" t="n">
-        <v>402.0704716648093</v>
+        <v>402.0914852917833</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26575,28 +26691,28 @@
         <v>0.1523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03146039014710923</v>
+        <v>0.02711207082137128</v>
       </c>
       <c r="J4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001440915075726745</v>
+        <v>0.001080040576597496</v>
       </c>
       <c r="M4" t="n">
-        <v>4.991117727223042</v>
+        <v>4.990917969037262</v>
       </c>
       <c r="N4" t="n">
-        <v>40.69839647016445</v>
+        <v>40.60936908595389</v>
       </c>
       <c r="O4" t="n">
-        <v>6.379529486581628</v>
+        <v>6.372548084240235</v>
       </c>
       <c r="P4" t="n">
-        <v>404.0962831613425</v>
+        <v>404.1390417424596</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26653,28 +26769,28 @@
         <v>0.1123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003959428916736707</v>
+        <v>0.0008641795482966277</v>
       </c>
       <c r="J5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K5" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L5" t="n">
-        <v>2.217203341736695e-05</v>
+        <v>1.066955359951827e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>4.965883207921757</v>
+        <v>4.958743931143915</v>
       </c>
       <c r="N5" t="n">
-        <v>41.95306116790392</v>
+        <v>41.80916537783624</v>
       </c>
       <c r="O5" t="n">
-        <v>6.477118276510312</v>
+        <v>6.466000725165149</v>
       </c>
       <c r="P5" t="n">
-        <v>409.7911608435923</v>
+        <v>409.8215967628538</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26731,28 +26847,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04452979501970039</v>
+        <v>0.04251011062058684</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K6" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003072478096281306</v>
+        <v>0.002831025167936763</v>
       </c>
       <c r="M6" t="n">
-        <v>4.852911501090963</v>
+        <v>4.840519790593417</v>
       </c>
       <c r="N6" t="n">
-        <v>38.17595324525428</v>
+        <v>38.0206677928691</v>
       </c>
       <c r="O6" t="n">
-        <v>6.178669213127878</v>
+        <v>6.166090154455179</v>
       </c>
       <c r="P6" t="n">
-        <v>427.5602089312248</v>
+        <v>427.5800684958705</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26809,28 +26925,28 @@
         <v>0.0931</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.008913709964115628</v>
+        <v>-0.01031207210863275</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K7" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001054478692269489</v>
+        <v>0.0001426947194714812</v>
       </c>
       <c r="M7" t="n">
-        <v>5.277684787719161</v>
+        <v>5.260653440121722</v>
       </c>
       <c r="N7" t="n">
-        <v>44.70407359421188</v>
+        <v>44.50740231881899</v>
       </c>
       <c r="O7" t="n">
-        <v>6.686110498205357</v>
+        <v>6.671386836244694</v>
       </c>
       <c r="P7" t="n">
-        <v>433.4246898511822</v>
+        <v>433.4384398953596</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26887,28 +27003,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02998494967567783</v>
+        <v>0.03001688285889035</v>
       </c>
       <c r="J8" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K8" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001274590385514807</v>
+        <v>0.001291806439299159</v>
       </c>
       <c r="M8" t="n">
-        <v>5.118416277967114</v>
+        <v>5.09566473181689</v>
       </c>
       <c r="N8" t="n">
-        <v>41.80188034192065</v>
+        <v>41.60855095968797</v>
       </c>
       <c r="O8" t="n">
-        <v>6.465437366638134</v>
+        <v>6.450469049587632</v>
       </c>
       <c r="P8" t="n">
-        <v>421.207770954923</v>
+        <v>421.2074579172277</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26965,28 +27081,28 @@
         <v>0.1391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04218036392378853</v>
+        <v>0.04215458197885068</v>
       </c>
       <c r="J9" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K9" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002973604322093815</v>
+        <v>0.003003664358755875</v>
       </c>
       <c r="M9" t="n">
-        <v>4.752516617173779</v>
+        <v>4.731353993182756</v>
       </c>
       <c r="N9" t="n">
-        <v>35.31674384610425</v>
+        <v>35.15375548784419</v>
       </c>
       <c r="O9" t="n">
-        <v>5.942789231169506</v>
+        <v>5.929060253349108</v>
       </c>
       <c r="P9" t="n">
-        <v>418.3429979863332</v>
+        <v>418.3432525479832</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27043,28 +27159,28 @@
         <v>0.1166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05466950565771475</v>
+        <v>0.05572676315168616</v>
       </c>
       <c r="J10" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K10" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00483449271337022</v>
+        <v>0.005078385187661572</v>
       </c>
       <c r="M10" t="n">
-        <v>4.88731303129856</v>
+        <v>4.870080604825294</v>
       </c>
       <c r="N10" t="n">
-        <v>36.42262414891184</v>
+        <v>36.26025523200092</v>
       </c>
       <c r="O10" t="n">
-        <v>6.035115918432043</v>
+        <v>6.021648879833572</v>
       </c>
       <c r="P10" t="n">
-        <v>418.4896385719226</v>
+        <v>418.4792328818954</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27121,28 +27237,28 @@
         <v>0.1266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1575557662780527</v>
+        <v>0.1594273928678762</v>
       </c>
       <c r="J11" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K11" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03699251702986028</v>
+        <v>0.03823959611988481</v>
       </c>
       <c r="M11" t="n">
-        <v>4.94846118283805</v>
+        <v>4.935174917563787</v>
       </c>
       <c r="N11" t="n">
-        <v>38.25788149844205</v>
+        <v>38.09951763718086</v>
       </c>
       <c r="O11" t="n">
-        <v>6.18529558699033</v>
+        <v>6.172480671268308</v>
       </c>
       <c r="P11" t="n">
-        <v>414.1046756380225</v>
+        <v>414.086254424563</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27199,28 +27315,28 @@
         <v>0.0862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09769189258642867</v>
+        <v>0.1003211014610307</v>
       </c>
       <c r="J12" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K12" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01335889156525794</v>
+        <v>0.01422328629536129</v>
       </c>
       <c r="M12" t="n">
-        <v>5.21067694903391</v>
+        <v>5.20038377295669</v>
       </c>
       <c r="N12" t="n">
-        <v>41.56841576065642</v>
+        <v>41.41199994910757</v>
       </c>
       <c r="O12" t="n">
-        <v>6.447357269506353</v>
+        <v>6.435215610149171</v>
       </c>
       <c r="P12" t="n">
-        <v>410.037582270372</v>
+        <v>410.01160959018</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27277,28 +27393,28 @@
         <v>0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3138315611207697</v>
+        <v>0.3165134069057362</v>
       </c>
       <c r="J13" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K13" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09614769310607174</v>
+        <v>0.09857999035325149</v>
       </c>
       <c r="M13" t="n">
-        <v>5.917369541579832</v>
+        <v>5.902213601189758</v>
       </c>
       <c r="N13" t="n">
-        <v>54.47188876571641</v>
+        <v>54.25704349636793</v>
       </c>
       <c r="O13" t="n">
-        <v>7.380507351511576</v>
+        <v>7.365938059498459</v>
       </c>
       <c r="P13" t="n">
-        <v>398.9004295983269</v>
+        <v>398.8738974095364</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27336,7 +27452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N432"/>
+  <dimension ref="A1:N434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58395,6 +58511,150 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-34.801406433328275,173.38883452588954</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-34.801455498625636,173.3897114073016</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-34.80144386202312,173.39056970429922</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-34.801287086767864,173.39143987737754</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-34.8010714242053,173.392271821564</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-34.8008747416826,173.39296013432116</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-34.80061160320121,173.39369986279263</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-34.80027803144932,173.39447919351858</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-34.799891016917236,173.3951619168543</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-34.7994552276322,173.39576849556155</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-34.798976972700956,173.39634570284622</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-34.798426263781316,173.396869937222</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-34.80140004118097,173.38883496696923</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-34.80145667069466,173.38971137987124</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-34.80144655855275,173.39056996784817</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-34.8012860998629,173.3914397564227</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-34.80106991149206,173.39227152028528</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-34.80087366197633,173.39295958076985</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-34.80061480177186,173.39370211080495</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-34.80028063898595,173.3944811486694</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-34.79989172809175,173.39516258899582</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-34.7994552276322,173.39576849556155</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-34.7989775200003,173.3963465716667</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-34.79842666653468,173.396870662784</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
